--- a/.xlsx files/worldbuilding_fifa_rankings_with_debuff.xlsx
+++ b/.xlsx files/worldbuilding_fifa_rankings_with_debuff.xlsx
@@ -2744,7 +2744,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">lasri</t>
+          <t xml:space="preserve">Lasri</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
